--- a/output/pdf_financials_xlsx/HUNT.xlsx
+++ b/output/pdf_financials_xlsx/HUNT.xlsx
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.272193</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.133954</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.414097</v>
       </c>
     </row>
     <row r="93">
@@ -3096,7 +3096,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3309,7 +3313,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.272193</v>
       </c>

--- a/output/pdf_financials_xlsx/HUNT.xlsx
+++ b/output/pdf_financials_xlsx/HUNT.xlsx
@@ -630,10 +630,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.016216</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.030593</v>
       </c>
     </row>
     <row r="13">
@@ -882,10 +882,10 @@
         <v>-1.812041</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>14.995463</v>
+        <v>14.979247</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.403609</v>
+        <v>-1.434202</v>
       </c>
     </row>
     <row r="28">
@@ -914,10 +914,10 @@
         <v>-1.812041</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>14.995463</v>
+        <v>14.979247</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.403609</v>
+        <v>-1.434202</v>
       </c>
     </row>
     <row r="30">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">

--- a/output/pdf_financials_xlsx/HUNT.xlsx
+++ b/output/pdf_financials_xlsx/HUNT.xlsx
@@ -541,13 +541,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.37305</v>
+        <v>0.38345</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.520096</v>
+        <v>0.536597</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.814361</v>
+        <v>0.867157</v>
       </c>
     </row>
     <row r="8">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>3.848531</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -3881,7 +3881,11 @@
           <t>Proceeds from sale of investments (note 4)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -5001,7 +5005,11 @@
           <t>Office expense</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>0.0104</v>
       </c>
